--- a/data/fmsForecastOutput/File1/RPT_RPT3223273375831MN_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT3223273375831MN_fmsForecastOutput.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1878,7 +1878,7 @@
         <v>424.9978955549008</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>459.3471523764514</v>
+        <v>459.3471523764515</v>
       </c>
       <c r="E8" s="149" t="n">
         <v>497.6939874785634</v>
@@ -1893,7 +1893,7 @@
         <v>43.81590767946712</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>49.39988838981795</v>
+        <v>49.39988838981796</v>
       </c>
       <c r="J8" s="149" t="n">
         <v>55.86605061778214</v>
@@ -1905,10 +1905,10 @@
         <v>72.22768689234549</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>54105255.78110533</v>
+        <v>54105255.78110534</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>61968274.46295174</v>
+        <v>61968274.46295175</v>
       </c>
       <c r="O8" s="152" t="n">
         <v>71069747.56810726</v>
@@ -1940,10 +1940,10 @@
         <v>701.0975762765187</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>54.2512545884915</v>
+        <v>54.25125458849151</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>61.15959929940809</v>
+        <v>61.1595992994081</v>
       </c>
       <c r="AA8" s="149" t="n">
         <v>69.15841598668581</v>
@@ -1955,10 +1955,10 @@
         <v>89.38933646815634</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>54105255.78110533</v>
+        <v>54105255.78110534</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>61968274.46295174</v>
+        <v>61968274.46295175</v>
       </c>
       <c r="AF8" s="152" t="n">
         <v>71069747.56810726</v>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>1468.837131009581</v>
+        <v>1468.83713100958</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>1580.617917402976</v>
+        <v>1580.617917402975</v>
       </c>
       <c r="E9" s="156" t="n">
         <v>1702.988649486066</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>1799.136298769263</v>
+        <v>1799.136298769262</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>1918.012212282228</v>
+        <v>1918.012212282227</v>
       </c>
       <c r="H9" s="155" t="n">
         <v>100.6143892093101</v>
@@ -2055,7 +2055,7 @@
         <v>27149485.45146079</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>29777210.07031593</v>
+        <v>29777210.07031592</v>
       </c>
       <c r="O9" s="159" t="n">
         <v>33381515.4286784</v>
@@ -2064,7 +2064,7 @@
         <v>37598302.51098073</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>43242042.11055609</v>
+        <v>43242042.11055607</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2084,13 +2084,13 @@
         <v>1823.264736781246</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>1943.734909779875</v>
+        <v>1943.734909779874</v>
       </c>
       <c r="Y9" s="155" t="n">
         <v>101.0285123397635</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>110.036028509595</v>
+        <v>110.0360285095949</v>
       </c>
       <c r="AA9" s="156" t="n">
         <v>122.5552382034352</v>
@@ -2099,13 +2099,13 @@
         <v>137.2649627502565</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>156.6312203645309</v>
+        <v>156.6312203645308</v>
       </c>
       <c r="AD9" s="158" t="n">
         <v>27149485.45146079</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>29777210.07031593</v>
+        <v>29777210.07031592</v>
       </c>
       <c r="AF9" s="159" t="n">
         <v>33381515.4286784</v>
@@ -2114,7 +2114,7 @@
         <v>37598302.51098073</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>43242042.11055609</v>
+        <v>43242042.11055607</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>557.3380190082815</v>
+        <v>557.3380190082814</v>
       </c>
       <c r="D10" s="162" t="n">
         <v>596.7416149535256</v>
@@ -2182,7 +2182,7 @@
         <v>685.6187301607029</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>738.6845892867386</v>
+        <v>738.6845892867384</v>
       </c>
       <c r="H10" s="161" t="n">
         <v>54.00176175699448</v>
@@ -2197,7 +2197,7 @@
         <v>75.94266948672937</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>86.8613906147085</v>
+        <v>86.86139061470848</v>
       </c>
       <c r="M10" s="164" t="n">
         <v>81254741.23256612</v>
@@ -2212,7 +2212,7 @@
         <v>118749476.8334717</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>137810201.1864503</v>
+        <v>137810201.1864502</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>660.9543181563653</v>
+        <v>660.9543181563652</v>
       </c>
       <c r="U10" s="162" t="n">
         <v>708.2699798521671</v>
@@ -2229,10 +2229,10 @@
         <v>763.6531134149484</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>814.0559147256938</v>
+        <v>814.0559147256937</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>877.0303824483393</v>
+        <v>877.0303824483391</v>
       </c>
       <c r="Y10" s="161" t="n">
         <v>64.18024422061214</v>
@@ -2247,7 +2247,7 @@
         <v>90.30536722908363</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>103.3051404224297</v>
+        <v>103.3051404224296</v>
       </c>
       <c r="AD10" s="164" t="n">
         <v>81254741.23256612</v>
@@ -2262,7 +2262,7 @@
         <v>118749476.8334717</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>137810201.1864503</v>
+        <v>137810201.1864502</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2342,7 +2342,7 @@
         <v>203.2365497739211</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>229.8523224258135</v>
+        <v>229.8523224258136</v>
       </c>
       <c r="L11" s="157" t="n">
         <v>263.6565114783326</v>
@@ -2351,13 +2351,13 @@
         <v>10376046.68896653</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>11743099.19389895</v>
+        <v>11743099.19389896</v>
       </c>
       <c r="O11" s="159" t="n">
         <v>13456684.86246902</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>15411868.61639159</v>
+        <v>15411868.6163916</v>
       </c>
       <c r="Q11" s="160" t="n">
         <v>17951939.57743408</v>
@@ -2368,16 +2368,16 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>1930.502684053506</v>
+        <v>1930.502684053505</v>
       </c>
       <c r="U11" s="156" t="n">
-        <v>2083.256283122923</v>
+        <v>2083.256283122924</v>
       </c>
       <c r="V11" s="156" t="n">
         <v>2264.560636143477</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>2430.024044184613</v>
+        <v>2430.024044184614</v>
       </c>
       <c r="X11" s="157" t="n">
         <v>2636.751950247583</v>
@@ -2386,13 +2386,13 @@
         <v>185.2117549341605</v>
       </c>
       <c r="Z11" s="156" t="n">
-        <v>206.8212572008017</v>
+        <v>206.8212572008018</v>
       </c>
       <c r="AA11" s="156" t="n">
         <v>234.0312203576259</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>264.9139632335062</v>
+        <v>264.9139632335063</v>
       </c>
       <c r="AC11" s="157" t="n">
         <v>304.1749410631306</v>
@@ -2401,13 +2401,13 @@
         <v>10376046.68896653</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>11743099.19389895</v>
+        <v>11743099.19389896</v>
       </c>
       <c r="AF11" s="159" t="n">
         <v>13456684.86246902</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>15411868.61639159</v>
+        <v>15411868.6163916</v>
       </c>
       <c r="AH11" s="160" t="n">
         <v>17951939.57743408</v>
@@ -2464,7 +2464,7 @@
         <v>599.4998377237779</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>642.2169656491465</v>
+        <v>642.2169656491463</v>
       </c>
       <c r="E12" s="162" t="n">
         <v>692.7640104987244</v>
@@ -2473,22 +2473,22 @@
         <v>739.0794543267651</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>796.7460324023087</v>
+        <v>796.7460324023086</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>58.39684634774519</v>
+        <v>58.39684634774517</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>65.02616570113477</v>
+        <v>65.02616570113476</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>73.14994826632231</v>
+        <v>73.1499482663223</v>
       </c>
       <c r="K12" s="162" t="n">
         <v>82.27103912789822</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>94.13649571300641</v>
+        <v>94.13649571300643</v>
       </c>
       <c r="M12" s="164" t="n">
         <v>91630787.92153265</v>
@@ -2609,13 +2609,13 @@
         <v>1563.747862346919</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>1621.319610285061</v>
+        <v>1621.31961028506</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>1658.83533257231</v>
+        <v>1658.835332572309</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>1722.970589399678</v>
+        <v>1722.970589399677</v>
       </c>
       <c r="H13" s="155" t="n">
         <v>1531.873884588692</v>
@@ -2630,22 +2630,22 @@
         <v>1573.312500371145</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>1640.497096024353</v>
+        <v>1640.497096024351</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>8305758.863287354</v>
+        <v>8305758.863287352</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>9094600.965851344</v>
+        <v>9094600.965851339</v>
       </c>
       <c r="O13" s="159" t="n">
         <v>10671201.6267484</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>12494903.11074286</v>
+        <v>12494903.11074285</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>14909967.45920723</v>
+        <v>14909967.45920722</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>1307.941244282315</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>1278.03006144494</v>
+        <v>1278.030061444939</v>
       </c>
       <c r="V13" s="156" t="n">
         <v>1325.082675441448</v>
@@ -2665,7 +2665,7 @@
         <v>1355.743769863643</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>1408.160651253237</v>
+        <v>1408.160651253236</v>
       </c>
       <c r="Y13" s="155" t="n">
         <v>1243.282040052269</v>
@@ -2677,25 +2677,25 @@
         <v>1240.146584247042</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>1275.098196191383</v>
+        <v>1275.098196191382</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>1330.343972035406</v>
+        <v>1330.343972035405</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>8305758.863287354</v>
+        <v>8305758.863287352</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>9094600.965851344</v>
+        <v>9094600.965851339</v>
       </c>
       <c r="AF13" s="159" t="n">
         <v>10671201.6267484</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>12494903.11074286</v>
+        <v>12494903.11074285</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>14909967.45920723</v>
+        <v>14909967.45920722</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>632.3682303313175</v>
+        <v>632.3682303313176</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>674.3179237214455</v>
+        <v>674.3179237214454</v>
       </c>
       <c r="E14" s="168" t="n">
         <v>727.3353954211973</v>
@@ -2758,13 +2758,13 @@
         <v>775.7239559723679</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>836.007140830195</v>
+        <v>836.0071408301948</v>
       </c>
       <c r="H14" s="167" t="n">
         <v>63.47083576004757</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>70.46936177401339</v>
+        <v>70.46936177401338</v>
       </c>
       <c r="J14" s="168" t="n">
         <v>79.42693043891836</v>
@@ -2776,7 +2776,7 @@
         <v>102.5840140052723</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>99936546.78482001</v>
+        <v>99936546.78482002</v>
       </c>
       <c r="N14" s="171" t="n">
         <v>112583184.693018</v>
@@ -2788,7 +2788,7 @@
         <v>146656248.5606062</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>170672108.2230916</v>
+        <v>170672108.2230915</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>742.1368818873068</v>
+        <v>742.1368818873067</v>
       </c>
       <c r="U14" s="168" t="n">
         <v>791.2366428989874</v>
@@ -2808,7 +2808,7 @@
         <v>908.4684907969926</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>977.8990839965313</v>
+        <v>977.8990839965312</v>
       </c>
       <c r="Y14" s="167" t="n">
         <v>75.21135024977916</v>
@@ -2823,10 +2823,10 @@
         <v>106.0457208449082</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>121.5408015229584</v>
+        <v>121.5408015229583</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>99936546.78482001</v>
+        <v>99936546.78482002</v>
       </c>
       <c r="AE14" s="171" t="n">
         <v>112583184.693018</v>
@@ -2838,7 +2838,7 @@
         <v>146656248.5606062</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>170672108.2230916</v>
+        <v>170672108.2230915</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>18483.6595414769</v>
       </c>
       <c r="D20" s="80" t="n">
-        <v>18838.96781281664</v>
+        <v>18838.96781281665</v>
       </c>
       <c r="E20" s="80" t="n">
         <v>19601.72514288477</v>
@@ -3301,7 +3301,7 @@
         <v>20897.97339795804</v>
       </c>
       <c r="G20" s="81" t="n">
-        <v>22545.23815523714</v>
+        <v>22545.23815523715</v>
       </c>
       <c r="H20" s="79" t="n">
         <v>251353.3455312388</v>
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="C22" s="79" t="n">
-        <v>7054.618257404902</v>
+        <v>7054.618257404903</v>
       </c>
       <c r="D22" s="80" t="n">
-        <v>7398.642443500064</v>
+        <v>7398.642443500065</v>
       </c>
       <c r="E22" s="80" t="n">
         <v>7799.488795923386</v>
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="T22" s="79" t="n">
-        <v>5374.790086890624</v>
+        <v>5374.790086890625</v>
       </c>
       <c r="U22" s="80" t="n">
-        <v>5636.896088605746</v>
+        <v>5636.896088605747</v>
       </c>
       <c r="V22" s="80" t="n">
         <v>5942.293903591652</v>
@@ -3706,7 +3706,7 @@
         <v>152845.3923681493</v>
       </c>
       <c r="D23" s="86" t="n">
-        <v>161142.7122959316</v>
+        <v>161142.7122959317</v>
       </c>
       <c r="E23" s="86" t="n">
         <v>170199.2974120757</v>
@@ -3736,10 +3736,10 @@
         <v>1569105.074200136</v>
       </c>
       <c r="N23" s="86" t="n">
-        <v>1591491.403672916</v>
+        <v>1591491.403672917</v>
       </c>
       <c r="O23" s="86" t="n">
-        <v>1611866.455871967</v>
+        <v>1611866.455871968</v>
       </c>
       <c r="P23" s="86" t="n">
         <v>1630723.847322466</v>
@@ -3954,7 +3954,7 @@
         <v>189057.26377468</v>
       </c>
       <c r="G25" s="93" t="n">
-        <v>204151.4957080462</v>
+        <v>204151.4957080463</v>
       </c>
       <c r="H25" s="91" t="n">
         <v>1416491.664904498</v>
@@ -3978,7 +3978,7 @@
         <v>1597618.906412952</v>
       </c>
       <c r="O25" s="92" t="n">
-        <v>1618835.686781125</v>
+        <v>1618835.686781126</v>
       </c>
       <c r="P25" s="92" t="n">
         <v>1638665.628187866</v>
@@ -4426,7 +4426,7 @@
         <v>45.05143788277217</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>51.98741723419373</v>
+        <v>51.98741723419374</v>
       </c>
       <c r="J35" s="149" t="n">
         <v>59.16741598746712</v>
@@ -4438,10 +4438,10 @@
         <v>77.66132655828368</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>55630927.19168363</v>
+        <v>55630927.19168364</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>65214125.87750943</v>
+        <v>65214125.87750944</v>
       </c>
       <c r="O35" s="152" t="n">
         <v>75269564.82490331</v>
@@ -4473,10 +4473,10 @@
         <v>753.8406691825293</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>55.78104290422424</v>
+        <v>55.78104290422425</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>64.36309291965483</v>
+        <v>64.36309291965485</v>
       </c>
       <c r="AA35" s="149" t="n">
         <v>73.24528443426564</v>
@@ -4488,10 +4488,10 @@
         <v>96.11403533701551</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>55630927.19168363</v>
+        <v>55630927.19168364</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>65214125.87750943</v>
+        <v>65214125.87750944</v>
       </c>
       <c r="AF35" s="152" t="n">
         <v>75269564.82490331</v>
@@ -4522,7 +4522,7 @@
         <v>1930.324084760244</v>
       </c>
       <c r="G36" s="157" t="n">
-        <v>2063.069599236236</v>
+        <v>2063.069599236235</v>
       </c>
       <c r="H36" s="155" t="n">
         <v>103.4865215066402</v>
@@ -4537,13 +4537,13 @@
         <v>146.6594394736739</v>
       </c>
       <c r="L36" s="157" t="n">
-        <v>167.7653079741257</v>
+        <v>167.7653079741256</v>
       </c>
       <c r="M36" s="158" t="n">
         <v>27924493.02874498</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>31347726.67879767</v>
+        <v>31347726.67879766</v>
       </c>
       <c r="O36" s="159" t="n">
         <v>35366836.91239465</v>
@@ -4552,7 +4552,7 @@
         <v>40339861.37275727</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>46512395.4456106</v>
+        <v>46512395.44561058</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>1531.027542089219</v>
       </c>
       <c r="U36" s="156" t="n">
-        <v>1686.299122621183</v>
+        <v>1686.299122621182</v>
       </c>
       <c r="V36" s="156" t="n">
         <v>1828.46895604642</v>
@@ -4572,13 +4572,13 @@
         <v>1956.211898292791</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>2090.737679177501</v>
+        <v>2090.7376791775</v>
       </c>
       <c r="Y36" s="155" t="n">
         <v>103.9124661710451</v>
       </c>
       <c r="Z36" s="156" t="n">
-        <v>115.8395745737698</v>
+        <v>115.8395745737697</v>
       </c>
       <c r="AA36" s="156" t="n">
         <v>129.8440489186674</v>
@@ -4593,7 +4593,7 @@
         <v>27924493.02874498</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>31347726.67879767</v>
+        <v>31347726.67879766</v>
       </c>
       <c r="AF36" s="159" t="n">
         <v>35366836.91239465</v>
@@ -4602,7 +4602,7 @@
         <v>40339861.37275727</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>46512395.4456106</v>
+        <v>46512395.44561058</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>573.1187088488806</v>
+        <v>573.1187088488805</v>
       </c>
       <c r="D37" s="162" t="n">
         <v>628.0687941264349</v>
@@ -4624,7 +4624,7 @@
         <v>735.4313419644</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>794.3479724169138</v>
+        <v>794.3479724169136</v>
       </c>
       <c r="H37" s="161" t="n">
         <v>55.53078906909032</v>
@@ -4639,7 +4639,7 @@
         <v>81.46017148611648</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>93.40680788092615</v>
+        <v>93.40680788092614</v>
       </c>
       <c r="M37" s="164" t="n">
         <v>83555420.22042862</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>679.6688410094621</v>
+        <v>679.668841009462</v>
       </c>
       <c r="U37" s="162" t="n">
         <v>745.4520700661197</v>
@@ -4671,10 +4671,10 @@
         <v>808.8732507362269</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>873.1999396522441</v>
+        <v>873.199939652244</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>943.1187764706978</v>
+        <v>943.1187764706975</v>
       </c>
       <c r="Y37" s="161" t="n">
         <v>65.9974691243457</v>
@@ -4723,7 +4723,7 @@
         <v>1827.748372003226</v>
       </c>
       <c r="F38" s="156" t="n">
-        <v>1986.18397988565</v>
+        <v>1986.183979885651</v>
       </c>
       <c r="G38" s="157" t="n">
         <v>2160.60368804572</v>
@@ -4732,13 +4732,13 @@
         <v>165.6055834336825</v>
       </c>
       <c r="I38" s="156" t="n">
-        <v>189.1797478488411</v>
+        <v>189.1797478488412</v>
       </c>
       <c r="J38" s="156" t="n">
         <v>215.3011134836874</v>
       </c>
       <c r="K38" s="156" t="n">
-        <v>246.5867919545622</v>
+        <v>246.5867919545623</v>
       </c>
       <c r="L38" s="157" t="n">
         <v>283.5674313083595</v>
@@ -4747,7 +4747,7 @@
         <v>10671082.92315376</v>
       </c>
       <c r="N38" s="159" t="n">
-        <v>12361143.15193073</v>
+        <v>12361143.15193074</v>
       </c>
       <c r="O38" s="159" t="n">
         <v>14255502.94920637</v>
@@ -4773,7 +4773,7 @@
         <v>2398.989881767719</v>
       </c>
       <c r="W38" s="156" t="n">
-        <v>2606.942697397956</v>
+        <v>2606.942697397957</v>
       </c>
       <c r="X38" s="157" t="n">
         <v>2835.875258064545</v>
@@ -4797,7 +4797,7 @@
         <v>10671082.92315376</v>
       </c>
       <c r="AE38" s="159" t="n">
-        <v>12361143.15193073</v>
+        <v>12361143.15193074</v>
       </c>
       <c r="AF38" s="159" t="n">
         <v>14255502.94920637</v>
@@ -4819,7 +4819,7 @@
         <v>616.4824577545969</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>675.9411837887241</v>
+        <v>675.9411837887239</v>
       </c>
       <c r="E39" s="162" t="n">
         <v>733.7980037844928</v>
@@ -4828,22 +4828,22 @@
         <v>792.7890633145136</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>856.7996496207121</v>
+        <v>856.799649620712</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>60.05111110332436</v>
+        <v>60.05111110332435</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>68.44083194974247</v>
+        <v>68.44083194974246</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>77.48278663627991</v>
+        <v>77.4827866362799</v>
       </c>
       <c r="K39" s="162" t="n">
         <v>88.24975402344384</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>101.2319023418733</v>
+        <v>101.2319023418734</v>
       </c>
       <c r="M39" s="164" t="n">
         <v>94226503.14358237</v>
@@ -4921,37 +4921,37 @@
         <v>1646.107819372303</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>1646.223668119717</v>
+        <v>1646.223668119716</v>
       </c>
       <c r="E40" s="156" t="n">
         <v>1717.863541306485</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>1779.866236665569</v>
+        <v>1779.866236665568</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>1853.254371732471</v>
+        <v>1853.25437173247</v>
       </c>
       <c r="H40" s="155" t="n">
         <v>1575.67772535352</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>1562.507990429555</v>
+        <v>1562.507990429554</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>1622.364738975186</v>
+        <v>1622.364738975185</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>1688.103541170757</v>
+        <v>1688.103541170756</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>1764.544579998228</v>
+        <v>1764.544579998227</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>8543261.533930626</v>
+        <v>8543261.533930624</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>9574271.992684856</v>
+        <v>9574271.99268485</v>
       </c>
       <c r="O40" s="159" t="n">
         <v>11306634.48479381</v>
@@ -4960,7 +4960,7 @@
         <v>13406548.40208461</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>16037396.42810286</v>
+        <v>16037396.42810285</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>1345.341744787405</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>1345.43642640798</v>
+        <v>1345.436426407979</v>
       </c>
       <c r="V40" s="156" t="n">
         <v>1403.986729647646</v>
@@ -4980,28 +4980,28 @@
         <v>1454.660697278587</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>1514.639831400706</v>
+        <v>1514.639831400705</v>
       </c>
       <c r="Y40" s="155" t="n">
         <v>1278.83361453638</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>1266.485950963123</v>
+        <v>1266.485950963122</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>1313.992990302016</v>
+        <v>1313.992990302015</v>
       </c>
       <c r="AB40" s="156" t="n">
         <v>1368.131111793329</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>1430.938982505546</v>
+        <v>1430.938982505545</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>8543261.533930626</v>
+        <v>8543261.533930624</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>9574271.992684856</v>
+        <v>9574271.99268485</v>
       </c>
       <c r="AF40" s="159" t="n">
         <v>11306634.48479381</v>
@@ -5010,7 +5010,7 @@
         <v>13406548.40208461</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>16037396.42810286</v>
+        <v>16037396.42810285</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5023,7 +5023,7 @@
         <v>650.2959759117505</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>709.7403732238347</v>
+        <v>709.7403732238346</v>
       </c>
       <c r="E41" s="180" t="n">
         <v>770.4360990094222</v>
@@ -5032,16 +5032,16 @@
         <v>832.1157498394167</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>899.0376971792157</v>
+        <v>899.0376971792156</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>65.27024461821777</v>
+        <v>65.27024461821776</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>74.17117262775653</v>
+        <v>74.17117262775652</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>84.13364017327403</v>
+        <v>84.13364017327402</v>
       </c>
       <c r="K41" s="180" t="n">
         <v>96.00343358786824</v>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>763.1765871826861</v>
+        <v>763.176587182686</v>
       </c>
       <c r="U41" s="186" t="n">
         <v>832.8009244367673</v>
@@ -5374,7 +5374,7 @@
         <v>0.1467119925647543</v>
       </c>
       <c r="D46" s="149" t="n">
-        <v>0.1646855323067668</v>
+        <v>0.1646855323067667</v>
       </c>
       <c r="E46" s="149" t="n">
         <v>0.1856576529803868</v>
@@ -5404,7 +5404,7 @@
         <v>18677.48044612669</v>
       </c>
       <c r="N46" s="152" t="n">
-        <v>22216.91854029268</v>
+        <v>22216.91854029267</v>
       </c>
       <c r="O46" s="152" t="n">
         <v>26511.5570277442</v>
@@ -5445,7 +5445,7 @@
         <v>0.02579856200590001</v>
       </c>
       <c r="AB46" s="149" t="n">
-        <v>0.03042799910542656</v>
+        <v>0.03042799910542657</v>
       </c>
       <c r="AC46" s="150" t="n">
         <v>0.03588068291344702</v>
@@ -5454,7 +5454,7 @@
         <v>18677.48044612669</v>
       </c>
       <c r="AE46" s="152" t="n">
-        <v>22216.91854029268</v>
+        <v>22216.91854029267</v>
       </c>
       <c r="AF46" s="152" t="n">
         <v>26511.5570277442</v>
@@ -5473,16 +5473,16 @@
         </is>
       </c>
       <c r="C47" s="155" t="n">
-        <v>0.03777039850405515</v>
+        <v>0.03777039850405514</v>
       </c>
       <c r="D47" s="156" t="n">
-        <v>0.03889587205484998</v>
+        <v>0.03889587205484997</v>
       </c>
       <c r="E47" s="156" t="n">
         <v>0.03928290586286613</v>
       </c>
       <c r="F47" s="156" t="n">
-        <v>0.03868030647827058</v>
+        <v>0.03868030647827057</v>
       </c>
       <c r="G47" s="157" t="n">
         <v>0.0375611677200474</v>
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="T47" s="155" t="n">
-        <v>0.03827694196027714</v>
+        <v>0.03827694196027713</v>
       </c>
       <c r="U47" s="156" t="n">
         <v>0.03941750937517945</v>
@@ -5535,7 +5535,7 @@
         <v>0.0391990528221601</v>
       </c>
       <c r="X47" s="157" t="n">
-        <v>0.03806490515651114</v>
+        <v>0.03806490515651113</v>
       </c>
       <c r="Y47" s="155" t="n">
         <v>0.002597896724412143</v>
@@ -5578,22 +5578,22 @@
         <v>0.1329001492104268</v>
       </c>
       <c r="D48" s="162" t="n">
-        <v>0.1492719468400522</v>
+        <v>0.1492719468400521</v>
       </c>
       <c r="E48" s="162" t="n">
         <v>0.1679901594943659</v>
       </c>
       <c r="F48" s="162" t="n">
-        <v>0.187562507470907</v>
+        <v>0.1875625074709071</v>
       </c>
       <c r="G48" s="163" t="n">
         <v>0.2080078113498099</v>
       </c>
       <c r="H48" s="161" t="n">
-        <v>0.01287700094083092</v>
+        <v>0.01287700094083093</v>
       </c>
       <c r="I48" s="162" t="n">
-        <v>0.0150376218048565</v>
+        <v>0.01503762180485649</v>
       </c>
       <c r="J48" s="162" t="n">
         <v>0.01765049650588027</v>
@@ -5614,7 +5614,7 @@
         <v>27281.56975128192</v>
       </c>
       <c r="P48" s="165" t="n">
-        <v>32485.91185734345</v>
+        <v>32485.91185734346</v>
       </c>
       <c r="Q48" s="166" t="n">
         <v>38806.27638130304</v>
@@ -5628,7 +5628,7 @@
         <v>0.1576079946251641</v>
       </c>
       <c r="U48" s="162" t="n">
-        <v>0.1771702125871201</v>
+        <v>0.17717021258712</v>
       </c>
       <c r="V48" s="162" t="n">
         <v>0.1994581499704282</v>
@@ -5643,13 +5643,13 @@
         <v>0.0153041130200634</v>
       </c>
       <c r="Z48" s="162" t="n">
-        <v>0.01787586800192747</v>
+        <v>0.01787586800192746</v>
       </c>
       <c r="AA48" s="162" t="n">
         <v>0.0209855589406025</v>
       </c>
       <c r="AB48" s="162" t="n">
-        <v>0.0247045484180368</v>
+        <v>0.02470454841803681</v>
       </c>
       <c r="AC48" s="163" t="n">
         <v>0.02908992074845245</v>
@@ -5664,7 +5664,7 @@
         <v>27281.56975128192</v>
       </c>
       <c r="AG48" s="165" t="n">
-        <v>32485.91185734345</v>
+        <v>32485.91185734346</v>
       </c>
       <c r="AH48" s="166" t="n">
         <v>38806.27638130304</v>
@@ -5683,7 +5683,7 @@
         <v>0.2004271686348618</v>
       </c>
       <c r="E49" s="156" t="n">
-        <v>0.2101127866742704</v>
+        <v>0.2101127866742705</v>
       </c>
       <c r="F49" s="156" t="n">
         <v>0.2186726436872586</v>
@@ -5695,13 +5695,13 @@
         <v>0.02096256863894909</v>
       </c>
       <c r="I49" s="156" t="n">
-        <v>0.02269470998490039</v>
+        <v>0.0226947099849004</v>
       </c>
       <c r="J49" s="156" t="n">
         <v>0.02475040745272295</v>
       </c>
       <c r="K49" s="156" t="n">
-        <v>0.02714843450613702</v>
+        <v>0.02714843450613703</v>
       </c>
       <c r="L49" s="157" t="n">
         <v>0.02986171123877625</v>
@@ -5736,7 +5736,7 @@
         <v>0.2757810960100279</v>
       </c>
       <c r="W49" s="156" t="n">
-        <v>0.287016236841274</v>
+        <v>0.2870162368412741</v>
       </c>
       <c r="X49" s="157" t="n">
         <v>0.2986382733545502</v>
@@ -5751,10 +5751,10 @@
         <v>0.02850062189577918</v>
       </c>
       <c r="AB49" s="156" t="n">
-        <v>0.03128965287234504</v>
+        <v>0.03128965287234505</v>
       </c>
       <c r="AC49" s="157" t="n">
-        <v>0.0344508246929659</v>
+        <v>0.03445082469296591</v>
       </c>
       <c r="AD49" s="158" t="n">
         <v>1350.759458651388</v>
@@ -5782,13 +5782,13 @@
         <v>0.1356035322383196</v>
       </c>
       <c r="D50" s="162" t="n">
-        <v>0.151620667361044</v>
+        <v>0.1516206673610439</v>
       </c>
       <c r="E50" s="162" t="n">
         <v>0.1699204551168507</v>
       </c>
       <c r="F50" s="162" t="n">
-        <v>0.1889891736798444</v>
+        <v>0.1889891736798445</v>
       </c>
       <c r="G50" s="163" t="n">
         <v>0.208900047628034</v>
@@ -5797,28 +5797,28 @@
         <v>0.01320904216821705</v>
       </c>
       <c r="I50" s="162" t="n">
-        <v>0.01535199343351229</v>
+        <v>0.01535199343351228</v>
       </c>
       <c r="J50" s="162" t="n">
-        <v>0.01794214525122255</v>
+        <v>0.01794214525122254</v>
       </c>
       <c r="K50" s="162" t="n">
-        <v>0.02103743462430134</v>
+        <v>0.02103743462430135</v>
       </c>
       <c r="L50" s="163" t="n">
-        <v>0.02468179022955405</v>
+        <v>0.02468179022955406</v>
       </c>
       <c r="M50" s="164" t="n">
         <v>20726.37509147294</v>
       </c>
       <c r="N50" s="165" t="n">
-        <v>24432.56557867787</v>
+        <v>24432.56557867786</v>
       </c>
       <c r="O50" s="165" t="n">
         <v>28920.34207682813</v>
       </c>
       <c r="P50" s="165" t="n">
-        <v>34306.24632833554</v>
+        <v>34306.24632833555</v>
       </c>
       <c r="Q50" s="166" t="n">
         <v>40839.51133852635</v>
@@ -5832,7 +5832,7 @@
         <v>0.1615332419358509</v>
       </c>
       <c r="U50" s="162" t="n">
-        <v>0.180752319846619</v>
+        <v>0.1807523198466189</v>
       </c>
       <c r="V50" s="162" t="n">
         <v>0.2026359184822089</v>
@@ -5862,13 +5862,13 @@
         <v>20726.37509147294</v>
       </c>
       <c r="AE50" s="165" t="n">
-        <v>24432.56557867787</v>
+        <v>24432.56557867786</v>
       </c>
       <c r="AF50" s="165" t="n">
         <v>28920.34207682813</v>
       </c>
       <c r="AG50" s="165" t="n">
-        <v>34306.24632833554</v>
+        <v>34306.24632833555</v>
       </c>
       <c r="AH50" s="166" t="n">
         <v>40839.51133852635</v>
@@ -5983,16 +5983,16 @@
         </is>
       </c>
       <c r="C52" s="179" t="n">
-        <v>0.1311502304156931</v>
+        <v>0.1311502304156932</v>
       </c>
       <c r="D52" s="180" t="n">
-        <v>0.1463390553138604</v>
+        <v>0.1463390553138603</v>
       </c>
       <c r="E52" s="180" t="n">
         <v>0.1635940860104685</v>
       </c>
       <c r="F52" s="180" t="n">
-        <v>0.1814595516902329</v>
+        <v>0.181459551690233</v>
       </c>
       <c r="G52" s="181" t="n">
         <v>0.2000451243175327</v>
@@ -6001,13 +6001,13 @@
         <v>0.01316355619295666</v>
       </c>
       <c r="I52" s="180" t="n">
-        <v>0.0152931124441529</v>
+        <v>0.01529311244415289</v>
       </c>
       <c r="J52" s="180" t="n">
-        <v>0.01786490272791862</v>
+        <v>0.01786490272791861</v>
       </c>
       <c r="K52" s="180" t="n">
-        <v>0.02093547685275697</v>
+        <v>0.02093547685275698</v>
       </c>
       <c r="L52" s="181" t="n">
         <v>0.02454695759452181</v>
@@ -6016,13 +6016,13 @@
         <v>20726.37509147294</v>
       </c>
       <c r="N52" s="183" t="n">
-        <v>24432.56557867787</v>
+        <v>24432.56557867786</v>
       </c>
       <c r="O52" s="183" t="n">
         <v>28920.34207682813</v>
       </c>
       <c r="P52" s="183" t="n">
-        <v>34306.24632833554</v>
+        <v>34306.24632833555</v>
       </c>
       <c r="Q52" s="184" t="n">
         <v>40839.51133852635</v>
@@ -6036,28 +6036,28 @@
         <v>0.1539157383167547</v>
       </c>
       <c r="U52" s="186" t="n">
-        <v>0.1717125094532997</v>
+        <v>0.1717125094532996</v>
       </c>
       <c r="V52" s="186" t="n">
         <v>0.1918125988746715</v>
       </c>
       <c r="W52" s="186" t="n">
-        <v>0.2125115304168805</v>
+        <v>0.2125115304168806</v>
       </c>
       <c r="X52" s="187" t="n">
         <v>0.2339979340772419</v>
       </c>
       <c r="Y52" s="185" t="n">
-        <v>0.01559848430394089</v>
+        <v>0.0155984843039409</v>
       </c>
       <c r="Z52" s="186" t="n">
-        <v>0.01812270478803463</v>
+        <v>0.01812270478803462</v>
       </c>
       <c r="AA52" s="186" t="n">
         <v>0.02116968340614471</v>
       </c>
       <c r="AB52" s="186" t="n">
-        <v>0.02480651630651728</v>
+        <v>0.02480651630651729</v>
       </c>
       <c r="AC52" s="187" t="n">
         <v>0.02908305869991512</v>
@@ -6066,13 +6066,13 @@
         <v>20726.37509147294</v>
       </c>
       <c r="AE52" s="189" t="n">
-        <v>24432.56557867787</v>
+        <v>24432.56557867786</v>
       </c>
       <c r="AF52" s="189" t="n">
         <v>28920.34207682813</v>
       </c>
       <c r="AG52" s="189" t="n">
-        <v>34306.24632833554</v>
+        <v>34306.24632833555</v>
       </c>
       <c r="AH52" s="190" t="n">
         <v>40839.51133852635</v>
@@ -6334,7 +6334,7 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.00831673783455289</v>
+        <v>0.008316737834552888</v>
       </c>
       <c r="D57" s="149" t="n">
         <v>0.00775530712793584</v>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.01011285538328334</v>
+        <v>0.01011285538328333</v>
       </c>
       <c r="U57" s="149" t="n">
         <v>0.009430175748948316</v>
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.00726232440155455</v>
+        <v>0.007262324401554549</v>
       </c>
       <c r="D59" s="162" t="n">
         <v>0.006805013685711213</v>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.008612483823732283</v>
+        <v>0.008612483823732281</v>
       </c>
       <c r="U59" s="162" t="n">
         <v>0.00807684060453496</v>
@@ -6745,7 +6745,7 @@
         <v>0.00692712995754408</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.006492570992111518</v>
+        <v>0.006492570992111516</v>
       </c>
       <c r="E61" s="162" t="n">
         <v>0.006075886650521905</v>
@@ -6757,13 +6757,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.0006747667277066883</v>
+        <v>0.0006747667277066882</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.0006573899783738695</v>
+        <v>0.0006573899783738694</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.0006415616103350306</v>
+        <v>0.0006415616103350305</v>
       </c>
       <c r="K61" s="162" t="n">
         <v>2.490053333870303e-05</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.008251715430144571</v>
+        <v>0.008251715430144569</v>
       </c>
       <c r="U61" s="162" t="n">
         <v>0.00774002178607045</v>
@@ -6949,7 +6949,7 @@
         <v>0.00669963882986987</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.006266406302521571</v>
+        <v>0.00626640630252157</v>
       </c>
       <c r="E63" s="180" t="n">
         <v>0.00584967314624834</v>
@@ -6961,13 +6961,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.0006724431358601232</v>
+        <v>0.0006724431358601231</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.0006548686268315282</v>
+        <v>0.0006548686268315281</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.0006387996308201321</v>
+        <v>0.000638799630820132</v>
       </c>
       <c r="K63" s="180" t="n">
         <v>2.477985308776845e-05</v>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.007862585171879584</v>
+        <v>0.007862585171879582</v>
       </c>
       <c r="U63" s="186" t="n">
         <v>0.007352926729998082</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>0.003655499133967393</v>
+        <v>0.003655499133967392</v>
       </c>
       <c r="U70" s="162" t="n">
         <v>0.005413824891538493</v>
@@ -7560,7 +7560,7 @@
         <v>0.007241634114256914</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.008956430157242221</v>
+        <v>0.008956430157242219</v>
       </c>
       <c r="X70" s="163" t="n">
         <v>0.01062844650463616</v>
@@ -7612,7 +7612,7 @@
         <v>0.02198198684610884</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>0.0277343437690152</v>
+        <v>0.02773434376901521</v>
       </c>
       <c r="G71" s="157" t="n">
         <v>0.03359134568995958</v>
@@ -7624,10 +7624,10 @@
         <v>0.0018299047241504</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>0.00258938610863807</v>
+        <v>0.002589386108638071</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>0.003443247416264124</v>
+        <v>0.003443247416264125</v>
       </c>
       <c r="L71" s="157" t="n">
         <v>0.004408680622085193</v>
@@ -7639,7 +7639,7 @@
         <v>119.5673136624068</v>
       </c>
       <c r="O71" s="159" t="n">
-        <v>171.4482601183611</v>
+        <v>171.4482601183612</v>
       </c>
       <c r="P71" s="159" t="n">
         <v>230.873789888811</v>
@@ -7662,7 +7662,7 @@
         <v>0.02885220133839797</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>0.03640239055795893</v>
+        <v>0.03640239055795894</v>
       </c>
       <c r="X71" s="157" t="n">
         <v>0.04408993035340669</v>
@@ -7689,7 +7689,7 @@
         <v>119.5673136624068</v>
       </c>
       <c r="AF71" s="159" t="n">
-        <v>171.4482601183611</v>
+        <v>171.4482601183612</v>
       </c>
       <c r="AG71" s="159" t="n">
         <v>230.873789888811</v>
@@ -7708,7 +7708,7 @@
         <v>0.00343489387564368</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.005093901337955695</v>
+        <v>0.005093901337955694</v>
       </c>
       <c r="E72" s="162" t="n">
         <v>0.006826981773771237</v>
@@ -7720,13 +7720,13 @@
         <v>0.01007815109724538</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.0003345905323984362</v>
+        <v>0.0003345905323984361</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.0005157709780094773</v>
+        <v>0.0005157709780094771</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.0007208708246939322</v>
+        <v>0.000720870824693932</v>
       </c>
       <c r="K72" s="162" t="n">
         <v>0.0009427609785245127</v>
@@ -7912,7 +7912,7 @@
         <v>0.003322089888133612</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.004916458439556846</v>
+        <v>0.004916458439556845</v>
       </c>
       <c r="E74" s="180" t="n">
         <v>0.00657280397890999</v>
@@ -7930,7 +7930,7 @@
         <v>0.0005137927915544359</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.0007177674119918336</v>
+        <v>0.0007177674119918335</v>
       </c>
       <c r="K74" s="180" t="n">
         <v>0.0009381918944044217</v>
@@ -7959,7 +7959,7 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.003898749672539853</v>
+        <v>0.003898749672539852</v>
       </c>
       <c r="U74" s="186" t="n">
         <v>0.005768913940769443</v>
@@ -8263,7 +8263,7 @@
         <v>437.1406345268638</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>483.5850484376496</v>
+        <v>483.5850484376497</v>
       </c>
       <c r="E79" s="149" t="n">
         <v>527.3047029857898</v>
@@ -8278,7 +8278,7 @@
         <v>45.06778477188595</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>52.00652120343759</v>
+        <v>52.0065212034376</v>
       </c>
       <c r="J79" s="149" t="n">
         <v>59.18984751502052</v>
@@ -8290,10 +8290,10 @@
         <v>77.69159413637969</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>55651112.84259372</v>
+        <v>55651112.84259373</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>65238090.30431327</v>
+        <v>65238090.30431328</v>
       </c>
       <c r="O79" s="152" t="n">
         <v>75298100.99281134</v>
@@ -8325,7 +8325,7 @@
         <v>754.1344696149661</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>55.80128302453692</v>
+        <v>55.80128302453693</v>
       </c>
       <c r="Z79" s="149" t="n">
         <v>64.38674461487251</v>
@@ -8340,10 +8340,10 @@
         <v>96.15149463882777</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>55651112.84259372</v>
+        <v>55651112.84259373</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>65238090.30431327</v>
+        <v>65238090.30431328</v>
       </c>
       <c r="AF79" s="152" t="n">
         <v>75298100.99281134</v>
@@ -8362,10 +8362,10 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>1510.804237725122</v>
+        <v>1510.804237725121</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>1664.022134777054</v>
+        <v>1664.022134777053</v>
       </c>
       <c r="E80" s="156" t="n">
         <v>1804.310930150772</v>
@@ -8374,7 +8374,7 @@
         <v>1930.362765066722</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>2063.107160403956</v>
+        <v>2063.107160403955</v>
       </c>
       <c r="H80" s="155" t="n">
         <v>103.4891087543993</v>
@@ -8389,13 +8389,13 @@
         <v>146.6623782714186</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>167.7683623843467</v>
+        <v>167.7683623843466</v>
       </c>
       <c r="M80" s="158" t="n">
         <v>27925191.16393168</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>31348459.43687936</v>
+        <v>31348459.43687935</v>
       </c>
       <c r="O80" s="159" t="n">
         <v>35367606.92511819</v>
@@ -8404,7 +8404,7 @@
         <v>40340669.71277308</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>46513242.27108224</v>
+        <v>46513242.27108222</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8415,22 +8415,22 @@
         <v>1531.065819031179</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>1686.338540130558</v>
+        <v>1686.338540130557</v>
       </c>
       <c r="V80" s="156" t="n">
         <v>1828.508765780161</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>1956.251097345614</v>
+        <v>1956.251097345613</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>2090.775744082658</v>
+        <v>2090.775744082657</v>
       </c>
       <c r="Y80" s="155" t="n">
         <v>103.9150640677695</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>115.8422823421933</v>
+        <v>115.8422823421932</v>
       </c>
       <c r="AA80" s="156" t="n">
         <v>129.846875905146</v>
@@ -8439,13 +8439,13 @@
         <v>147.2768757000928</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>168.4801536755408</v>
+        <v>168.4801536755407</v>
       </c>
       <c r="AD80" s="158" t="n">
         <v>27925191.16393168</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>31348459.43687936</v>
+        <v>31348459.43687935</v>
       </c>
       <c r="AF80" s="159" t="n">
         <v>35367606.92511819</v>
@@ -8454,7 +8454,7 @@
         <v>40340669.71277308</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>46513242.27108224</v>
+        <v>46513242.27108222</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8479,7 +8479,7 @@
         <v>794.5649321070103</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>55.54466839753658</v>
+        <v>55.54466839753659</v>
       </c>
       <c r="I81" s="162" t="n">
         <v>63.28768942446047</v>
@@ -8494,7 +8494,7 @@
         <v>93.43232001514751</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>83576304.0065254</v>
+        <v>83576304.00652541</v>
       </c>
       <c r="N81" s="165" t="n">
         <v>96586549.74119264</v>
@@ -8523,13 +8523,13 @@
         <v>809.0875110088125</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>873.4318730997878</v>
+        <v>873.4318730997876</v>
       </c>
       <c r="X81" s="163" t="n">
         <v>943.3763698234507</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>66.01396448783602</v>
+        <v>66.01396448783603</v>
       </c>
       <c r="Z81" s="162" t="n">
         <v>75.2327992404536</v>
@@ -8544,7 +8544,7 @@
         <v>111.1200139768864</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>83576304.0065254</v>
+        <v>83576304.00652541</v>
       </c>
       <c r="AE81" s="165" t="n">
         <v>96586549.74119264</v>
@@ -8575,7 +8575,7 @@
         <v>1827.980466776747</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>1986.430386873106</v>
+        <v>1986.430386873107</v>
       </c>
       <c r="G82" s="157" t="n">
         <v>2160.864806661154</v>
@@ -8590,7 +8590,7 @@
         <v>215.3284532772487</v>
       </c>
       <c r="K82" s="156" t="n">
-        <v>246.6173836364846</v>
+        <v>246.6173836364847</v>
       </c>
       <c r="L82" s="157" t="n">
         <v>283.6017017002203</v>
@@ -8634,13 +8634,13 @@
         <v>190.5035931516384</v>
       </c>
       <c r="Z82" s="156" t="n">
-        <v>217.7345645236692</v>
+        <v>217.7345645236693</v>
       </c>
       <c r="AA82" s="156" t="n">
         <v>247.9553050583274</v>
       </c>
       <c r="AB82" s="156" t="n">
-        <v>284.236364514027</v>
+        <v>284.2363645140271</v>
       </c>
       <c r="AC82" s="157" t="n">
         <v>327.1852851893525</v>
@@ -8668,19 +8668,19 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>616.6284233106684</v>
+        <v>616.6284233106685</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>676.1043909284153</v>
+        <v>676.1043909284152</v>
       </c>
       <c r="E83" s="162" t="n">
         <v>733.9808271080338</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>792.9867454468548</v>
+        <v>792.9867454468549</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>857.0186278194374</v>
+        <v>857.0186278194373</v>
       </c>
       <c r="H83" s="161" t="n">
         <v>60.06532950275268</v>
@@ -8689,16 +8689,16 @@
         <v>68.45735710413237</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>77.50209121396615</v>
+        <v>77.50209121396614</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>88.27175911958001</v>
+        <v>88.27175911958003</v>
       </c>
       <c r="L83" s="163" t="n">
         <v>101.2577748776968</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>94248813.30627236</v>
+        <v>94248813.30627237</v>
       </c>
       <c r="N83" s="165" t="n">
         <v>108949295.3493937</v>
@@ -8718,7 +8718,7 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>734.5383017907646</v>
+        <v>734.5383017907648</v>
       </c>
       <c r="U83" s="162" t="n">
         <v>806.0077774739783</v>
@@ -8727,13 +8727,13 @@
         <v>875.2970850218634</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>945.674184541223</v>
+        <v>945.6741845412231</v>
       </c>
       <c r="X83" s="163" t="n">
         <v>1021.984688495066</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>71.28923330475507</v>
+        <v>71.28923330475509</v>
       </c>
       <c r="Z83" s="162" t="n">
         <v>81.26816850212755</v>
@@ -8748,7 +8748,7 @@
         <v>120.2740493351916</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>94248813.30627236</v>
+        <v>94248813.30627237</v>
       </c>
       <c r="AE83" s="165" t="n">
         <v>108949295.3493937</v>
@@ -8773,37 +8773,37 @@
         <v>1646.107819372303</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>1646.223668119717</v>
+        <v>1646.223668119716</v>
       </c>
       <c r="E84" s="156" t="n">
         <v>1717.863541306485</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>1779.866236665569</v>
+        <v>1779.866236665568</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>1853.254371732471</v>
+        <v>1853.25437173247</v>
       </c>
       <c r="H84" s="155" t="n">
         <v>1575.67772535352</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>1562.507990429555</v>
+        <v>1562.507990429554</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>1622.364738975186</v>
+        <v>1622.364738975185</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>1688.103541170757</v>
+        <v>1688.103541170756</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>1764.544579998228</v>
+        <v>1764.544579998227</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>8543261.533930626</v>
+        <v>8543261.533930624</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>9574271.992684856</v>
+        <v>9574271.99268485</v>
       </c>
       <c r="O84" s="159" t="n">
         <v>11306634.48479381</v>
@@ -8812,7 +8812,7 @@
         <v>13406548.40208461</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>16037396.42810286</v>
+        <v>16037396.42810285</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>1345.341744787405</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>1345.43642640798</v>
+        <v>1345.436426407979</v>
       </c>
       <c r="V84" s="156" t="n">
         <v>1403.986729647646</v>
@@ -8832,28 +8832,28 @@
         <v>1454.660697278587</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>1514.639831400706</v>
+        <v>1514.639831400705</v>
       </c>
       <c r="Y84" s="155" t="n">
         <v>1278.83361453638</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>1266.485950963123</v>
+        <v>1266.485950963122</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>1313.992990302016</v>
+        <v>1313.992990302015</v>
       </c>
       <c r="AB84" s="156" t="n">
         <v>1368.131111793329</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>1430.938982505546</v>
+        <v>1430.938982505545</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>8543261.533930626</v>
+        <v>8543261.533930624</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>9574271.992684856</v>
+        <v>9574271.99268485</v>
       </c>
       <c r="AF84" s="159" t="n">
         <v>11306634.48479381</v>
@@ -8862,7 +8862,7 @@
         <v>13406548.40208461</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>16037396.42810286</v>
+        <v>16037396.42810285</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8875,28 +8875,28 @@
         <v>650.4371478708842</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>709.8978951438908</v>
+        <v>709.8978951438907</v>
       </c>
       <c r="E85" s="180" t="n">
         <v>770.6121155725576</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>832.3055560088037</v>
+        <v>832.3055560088039</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>899.2473932586768</v>
+        <v>899.2473932586767</v>
       </c>
       <c r="H85" s="179" t="n">
         <v>65.28441405590031</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>74.18763440161908</v>
+        <v>74.18763440161906</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>84.15286164304474</v>
+        <v>84.15286164304473</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>96.0253320364685</v>
+        <v>96.02533203646851</v>
       </c>
       <c r="L85" s="181" t="n">
         <v>110.3440421485463</v>
@@ -8922,7 +8922,7 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>763.3422642558473</v>
+        <v>763.3422642558472</v>
       </c>
       <c r="U85" s="186" t="n">
         <v>832.9857587868914</v>
@@ -8931,7 +8931,7 @@
         <v>903.5357953148888</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>974.7325276315221</v>
+        <v>974.7325276315223</v>
       </c>
       <c r="X85" s="187" t="n">
         <v>1051.872836015096</v>
@@ -9407,7 +9407,7 @@
         <v>18483.6595414769</v>
       </c>
       <c r="D91" s="80" t="n">
-        <v>18838.96781281664</v>
+        <v>18838.96781281665</v>
       </c>
       <c r="E91" s="80" t="n">
         <v>19601.72514288477</v>
@@ -9416,7 +9416,7 @@
         <v>20897.97339795804</v>
       </c>
       <c r="G91" s="81" t="n">
-        <v>22545.23815523714</v>
+        <v>22545.23815523715</v>
       </c>
       <c r="H91" s="79" t="n">
         <v>251353.3455312388</v>
@@ -9636,10 +9636,10 @@
         </is>
       </c>
       <c r="C93" s="79" t="n">
-        <v>7054.618257404902</v>
+        <v>7054.618257404903</v>
       </c>
       <c r="D93" s="80" t="n">
-        <v>7398.642443500064</v>
+        <v>7398.642443500065</v>
       </c>
       <c r="E93" s="80" t="n">
         <v>7799.488795923386</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="T93" s="79" t="n">
-        <v>5374.790086890624</v>
+        <v>5374.790086890625</v>
       </c>
       <c r="U93" s="80" t="n">
-        <v>5636.896088605746</v>
+        <v>5636.896088605747</v>
       </c>
       <c r="V93" s="80" t="n">
         <v>5942.293903591652</v>
@@ -9759,7 +9759,7 @@
         <v>152845.3923681493</v>
       </c>
       <c r="D94" s="86" t="n">
-        <v>161142.7122959316</v>
+        <v>161142.7122959317</v>
       </c>
       <c r="E94" s="86" t="n">
         <v>170199.2974120757</v>
@@ -9789,10 +9789,10 @@
         <v>1569105.074200136</v>
       </c>
       <c r="N94" s="86" t="n">
-        <v>1591491.403672916</v>
+        <v>1591491.403672917</v>
       </c>
       <c r="O94" s="86" t="n">
-        <v>1611866.455871967</v>
+        <v>1611866.455871968</v>
       </c>
       <c r="P94" s="86" t="n">
         <v>1630723.847322466</v>
@@ -10000,7 +10000,7 @@
         <v>189057.26377468</v>
       </c>
       <c r="G96" s="134" t="n">
-        <v>204151.4957080462</v>
+        <v>204151.4957080463</v>
       </c>
       <c r="H96" s="132" t="n">
         <v>1416491.664904498</v>
@@ -10024,7 +10024,7 @@
         <v>1597618.906412952</v>
       </c>
       <c r="O96" s="133" t="n">
-        <v>1618835.686781125</v>
+        <v>1618835.686781126</v>
       </c>
       <c r="P96" s="133" t="n">
         <v>1638665.628187866</v>
